--- a/SGC-CKN/Excel/dba7d8c3-bd10-41ad-93e0-e7d938c7d8a6_Lô_CT-02_P1_124_D800_01-04-2026.xlsx
+++ b/SGC-CKN/Excel/dba7d8c3-bd10-41ad-93e0-e7d938c7d8a6_Lô_CT-02_P1_124_D800_01-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P1_124</t>
+    <t>P1-124</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
